--- a/03_Outputs/Agroindustrial_Occidente/10_Seguridad/seguridad.xlsx
+++ b/03_Outputs/Agroindustrial_Occidente/10_Seguridad/seguridad.xlsx
@@ -19,20 +19,23 @@
     <sheet name="P6_cambio_municipio" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="irv" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="desaparecidos" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="_fig_01" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="_fig_02" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="_fig_03" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="_fig_04" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="_fig_05" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="_mapa10_homicidios" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="_mapa10_homicidios_dpto" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="reparacion_colectiva" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="reparacion_colectiva_sujetos" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="_fig_01" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="_fig_02" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="_fig_03" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="_fig_04" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="_fig_05" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="_fig_06" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="_mapa10_homicidios" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="_mapa10_homicidios_dpto" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="73">
+  <numFmts count="80">
     <numFmt numFmtId="165" formatCode="#,##0.00"/>
     <numFmt numFmtId="166" formatCode="#,##0.00"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
@@ -106,8 +109,15 @@
     <numFmt numFmtId="235" formatCode="#,##0"/>
     <numFmt numFmtId="236" formatCode="0.0%"/>
     <numFmt numFmtId="237" formatCode="0.0%"/>
+    <numFmt numFmtId="238" formatCode="#,##0"/>
+    <numFmt numFmtId="239" formatCode="#,##0"/>
+    <numFmt numFmtId="240" formatCode="#,##0"/>
+    <numFmt numFmtId="241" formatCode="#,##0"/>
+    <numFmt numFmtId="242" formatCode="0.0%"/>
+    <numFmt numFmtId="243" formatCode="0.0%"/>
+    <numFmt numFmtId="244" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -117,23 +127,307 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Aptos Narrow"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="25">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -153,7 +447,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="135">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0"/>
     <xf applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0"/>
@@ -164,73 +458,131 @@
     <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="168" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="169" xfId="0"/>
     <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="170" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="171" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="172" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="172" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="173" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="174" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="174" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="175" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="176" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="176" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="177" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="178" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="178" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="179" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="180" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="180" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="4" fontId="5" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="181" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="182" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="182" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="183" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="184" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="184" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="185" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="186" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="186" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="187" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="188" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="188" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="5" fontId="7" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="189" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="190" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="190" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="191" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="192" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="192" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="193" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="194" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="194" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="195" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="196" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="196" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="197" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="198" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="198" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="6" fontId="9" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="199" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="200" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="7" fontId="10" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="201" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="202" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="11" numFmtId="202" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="203" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="204" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="11" numFmtId="204" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="205" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="206" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="11" numFmtId="206" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="8" fontId="12" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="207" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="208" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="13" numFmtId="208" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="209" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="210" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="13" numFmtId="210" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="211" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="212" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="13" numFmtId="212" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="9" fontId="14" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="213" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="214" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="215" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="216" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="217" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="10" fontId="15" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="218" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="219" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="220" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="221" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="222" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="16" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="11" fontId="16" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="223" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="224" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="225" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="226" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="227" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="17" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="12" fontId="17" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="228" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="229" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="230" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="231" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="232" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="18" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="13" fontId="18" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="233" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="19" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="14" fontId="19" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="20" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="234" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="235" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="20" numFmtId="235" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="236" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="237" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="20" numFmtId="237" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="21" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="15" fontId="21" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="22" numFmtId="0" xfId="0"/>
+    <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="238" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="22" numFmtId="239" xfId="0"/>
+    <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="240" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="22" numFmtId="241" xfId="0"/>
+    <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="242" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="22" numFmtId="243" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="23" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="16" fontId="23" numFmtId="0" xfId="0"/>
+    <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="244" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="24" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="17" fontId="24" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="25" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="18" fontId="25" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="26" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="19" fontId="26" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="27" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="20" fontId="27" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="28" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="21" fontId="28" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="29" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="22" fontId="29" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="30" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="23" fontId="30" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="31" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="24" fontId="31" numFmtId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -559,13 +911,13 @@
   <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="44.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="45.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="45.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="34.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="46.711"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -677,47 +1029,47 @@
   <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="84" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="84" t="inlineStr">
         <is>
           <t>Periodo</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="84" t="inlineStr">
         <is>
           <t>N respuestas</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="84" t="inlineStr">
         <is>
           <t>Muy seguro (%)</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="84" t="inlineStr">
         <is>
           <t>Seguro (%)</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="84" t="inlineStr">
         <is>
           <t>Inseguro (%)</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="84" t="inlineStr">
         <is>
           <t>Muy inseguro (%)</t>
         </is>
@@ -734,19 +1086,19 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="C2" s="66">
+      <c r="C2" s="89">
         <v>192</v>
       </c>
-      <c r="D2" s="62">
+      <c r="D2" s="85">
         <v>0.100551557057243</v>
       </c>
-      <c r="E2" s="63">
+      <c r="E2" s="86">
         <v>0.739512245479396</v>
       </c>
-      <c r="F2" s="64">
+      <c r="F2" s="87">
         <v>0.146335874140359</v>
       </c>
-      <c r="G2" s="65">
+      <c r="G2" s="88">
         <v>0.0136003233230018</v>
       </c>
     </row>
@@ -761,19 +1113,19 @@
           <t>2019 (1)</t>
         </is>
       </c>
-      <c r="C3" s="66">
+      <c r="C3" s="89">
         <v>192</v>
       </c>
-      <c r="D3" s="62">
+      <c r="D3" s="85">
         <v>0.159461463918289</v>
       </c>
-      <c r="E3" s="63">
+      <c r="E3" s="86">
         <v>0.71049641555186</v>
       </c>
-      <c r="F3" s="64">
+      <c r="F3" s="87">
         <v>0.12382681433565</v>
       </c>
-      <c r="G3" s="65">
+      <c r="G3" s="88">
         <v>0.00621530619420113</v>
       </c>
     </row>
@@ -788,19 +1140,19 @@
           <t>2019 (2)</t>
         </is>
       </c>
-      <c r="C4" s="66">
+      <c r="C4" s="89">
         <v>192</v>
       </c>
-      <c r="D4" s="62">
+      <c r="D4" s="85">
         <v>0.128059143995578</v>
       </c>
-      <c r="E4" s="63">
+      <c r="E4" s="86">
         <v>0.770126058188632</v>
       </c>
-      <c r="F4" s="64">
+      <c r="F4" s="87">
         <v>0.0981163870754932</v>
       </c>
-      <c r="G4" s="65">
+      <c r="G4" s="88">
         <v>0.0036984107402976</v>
       </c>
     </row>
@@ -815,19 +1167,19 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="C5" s="66">
+      <c r="C5" s="89">
         <v>216</v>
       </c>
-      <c r="D5" s="62">
+      <c r="D5" s="85">
         <v>0.137214728456845</v>
       </c>
-      <c r="E5" s="63">
+      <c r="E5" s="86">
         <v>0.741980189750686</v>
       </c>
-      <c r="F5" s="64">
+      <c r="F5" s="87">
         <v>0.0871326643399958</v>
       </c>
-      <c r="G5" s="65">
+      <c r="G5" s="88">
         <v>0.0336724174524726</v>
       </c>
     </row>
@@ -842,19 +1194,19 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="C6" s="66">
+      <c r="C6" s="89">
         <v>216</v>
       </c>
-      <c r="D6" s="62">
+      <c r="D6" s="85">
         <v>0.113178570294933</v>
       </c>
-      <c r="E6" s="63">
+      <c r="E6" s="86">
         <v>0.7091105346085</v>
       </c>
-      <c r="F6" s="64">
+      <c r="F6" s="87">
         <v>0.127335682188481</v>
       </c>
-      <c r="G6" s="65">
+      <c r="G6" s="88">
         <v>0.050375212908085</v>
       </c>
     </row>
@@ -869,19 +1221,19 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="C7" s="66">
+      <c r="C7" s="89">
         <v>216</v>
       </c>
-      <c r="D7" s="62">
+      <c r="D7" s="85">
         <v>0.0843217131082108</v>
       </c>
-      <c r="E7" s="63">
+      <c r="E7" s="86">
         <v>0.774073497144105</v>
       </c>
-      <c r="F7" s="64">
+      <c r="F7" s="87">
         <v>0.101886959482109</v>
       </c>
-      <c r="G7" s="65">
+      <c r="G7" s="88">
         <v>0.0397178302655748</v>
       </c>
     </row>
@@ -896,19 +1248,19 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="C8" s="66">
+      <c r="C8" s="89">
         <v>208</v>
       </c>
-      <c r="D8" s="62">
+      <c r="D8" s="85">
         <v>0.105135027816389</v>
       </c>
-      <c r="E8" s="63">
+      <c r="E8" s="86">
         <v>0.822187127054693</v>
       </c>
-      <c r="F8" s="64">
+      <c r="F8" s="87">
         <v>0.0726778451289176</v>
       </c>
-      <c r="G8" s="65">
+      <c r="G8" s="88">
         <v>0</v>
       </c>
     </row>
@@ -923,19 +1275,19 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="C9" s="66">
+      <c r="C9" s="89">
         <v>216</v>
       </c>
-      <c r="D9" s="62">
+      <c r="D9" s="85">
         <v>0.076138289061366</v>
       </c>
-      <c r="E9" s="63">
+      <c r="E9" s="86">
         <v>0.8149911926835</v>
       </c>
-      <c r="F9" s="64">
+      <c r="F9" s="87">
         <v>0.0908055441901596</v>
       </c>
-      <c r="G9" s="65">
+      <c r="G9" s="88">
         <v>0.0180649740649741</v>
       </c>
     </row>
@@ -951,47 +1303,47 @@
   <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="91" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="91" t="inlineStr">
         <is>
           <t>Periodo</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="91" t="inlineStr">
         <is>
           <t>N respuestas</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="91" t="inlineStr">
         <is>
           <t>Más seguro (%)</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="91" t="inlineStr">
         <is>
           <t>Menos seguro (%)</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="91" t="inlineStr">
         <is>
           <t>Igual (%)</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="91" t="inlineStr">
         <is>
           <t>No sabe/No responde (%)</t>
         </is>
@@ -1008,19 +1360,19 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="C2" s="71">
+      <c r="C2" s="96">
         <v>192</v>
       </c>
-      <c r="D2" s="67">
+      <c r="D2" s="92">
         <v>0.127793696936544</v>
       </c>
-      <c r="E2" s="68">
+      <c r="E2" s="93">
         <v>0.0510702222098586</v>
       </c>
-      <c r="F2" s="69">
+      <c r="F2" s="94">
         <v>0.801923596330404</v>
       </c>
-      <c r="G2" s="70">
+      <c r="G2" s="95">
         <v>0.019212484523193</v>
       </c>
     </row>
@@ -1035,19 +1387,19 @@
           <t>2019 (1)</t>
         </is>
       </c>
-      <c r="C3" s="71">
+      <c r="C3" s="96">
         <v>192</v>
       </c>
-      <c r="D3" s="67">
+      <c r="D3" s="92">
         <v>0.322086118234861</v>
       </c>
-      <c r="E3" s="68">
+      <c r="E3" s="93">
         <v>0.0938445361319863</v>
       </c>
-      <c r="F3" s="69">
+      <c r="F3" s="94">
         <v>0.582338123291686</v>
       </c>
-      <c r="G3" s="70">
+      <c r="G3" s="95">
         <v>0.00173122234146641</v>
       </c>
     </row>
@@ -1062,19 +1414,19 @@
           <t>2019 (2)</t>
         </is>
       </c>
-      <c r="C4" s="71">
+      <c r="C4" s="96">
         <v>192</v>
       </c>
-      <c r="D4" s="67">
+      <c r="D4" s="92">
         <v>0.1423105549653</v>
       </c>
-      <c r="E4" s="68">
+      <c r="E4" s="93">
         <v>0.0510434020534527</v>
       </c>
-      <c r="F4" s="69">
+      <c r="F4" s="94">
         <v>0.792096255212188</v>
       </c>
-      <c r="G4" s="70">
+      <c r="G4" s="95">
         <v>0.0145497877690588</v>
       </c>
     </row>
@@ -1089,19 +1441,19 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="C5" s="71">
+      <c r="C5" s="96">
         <v>216</v>
       </c>
-      <c r="D5" s="67">
+      <c r="D5" s="92">
         <v>0.211299359555173</v>
       </c>
-      <c r="E5" s="68">
+      <c r="E5" s="93">
         <v>0.0657537864623005</v>
       </c>
-      <c r="F5" s="69">
+      <c r="F5" s="94">
         <v>0.719793944394851</v>
       </c>
-      <c r="G5" s="70">
+      <c r="G5" s="95">
         <v>0.00315290958767506</v>
       </c>
     </row>
@@ -1116,19 +1468,19 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="C6" s="71">
+      <c r="C6" s="96">
         <v>216</v>
       </c>
-      <c r="D6" s="67">
+      <c r="D6" s="92">
         <v>0.14416294727335</v>
       </c>
-      <c r="E6" s="68">
+      <c r="E6" s="93">
         <v>0.0856772238624814</v>
       </c>
-      <c r="F6" s="69">
+      <c r="F6" s="94">
         <v>0.770159828864169</v>
       </c>
-      <c r="G6" s="70">
+      <c r="G6" s="95">
         <v>0</v>
       </c>
     </row>
@@ -1143,19 +1495,19 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="C7" s="71">
+      <c r="C7" s="96">
         <v>216</v>
       </c>
-      <c r="D7" s="67">
+      <c r="D7" s="92">
         <v>0.130045782960027</v>
       </c>
-      <c r="E7" s="68">
+      <c r="E7" s="93">
         <v>0.0737799461608271</v>
       </c>
-      <c r="F7" s="69">
+      <c r="F7" s="94">
         <v>0.796174270879146</v>
       </c>
-      <c r="G7" s="70">
+      <c r="G7" s="95">
         <v>0</v>
       </c>
     </row>
@@ -1170,19 +1522,19 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="C8" s="71">
+      <c r="C8" s="96">
         <v>208</v>
       </c>
-      <c r="D8" s="67">
+      <c r="D8" s="92">
         <v>0.172617487058501</v>
       </c>
-      <c r="E8" s="68">
+      <c r="E8" s="93">
         <v>0.0404051460501737</v>
       </c>
-      <c r="F8" s="69">
+      <c r="F8" s="94">
         <v>0.786530945312716</v>
       </c>
-      <c r="G8" s="70">
+      <c r="G8" s="95">
         <v>0.000446421578609357</v>
       </c>
     </row>
@@ -1197,19 +1549,19 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="C9" s="71">
+      <c r="C9" s="96">
         <v>216</v>
       </c>
-      <c r="D9" s="67">
+      <c r="D9" s="92">
         <v>0.222517276440353</v>
       </c>
-      <c r="E9" s="68">
+      <c r="E9" s="93">
         <v>0.0714355868202022</v>
       </c>
-      <c r="F9" s="69">
+      <c r="F9" s="94">
         <v>0.706047136739444</v>
       </c>
-      <c r="G9" s="70">
+      <c r="G9" s="95">
         <v>0</v>
       </c>
     </row>
@@ -1225,40 +1577,40 @@
   <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="1" max="2" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="34.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="98" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="98" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="98" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="98" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="98" t="inlineStr">
         <is>
           <t>Índice de Riesgo de Victimización</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="98" t="inlineStr">
         <is>
           <t>Categoría de riesgo</t>
         </is>
@@ -1283,7 +1635,7 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E2" s="72">
+      <c r="E2" s="99">
         <v>0.10453732</v>
       </c>
       <c r="F2" t="inlineStr">
@@ -1311,7 +1663,7 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E3" s="72">
+      <c r="E3" s="99">
         <v>0.22323643</v>
       </c>
       <c r="F3" t="inlineStr">
@@ -1339,7 +1691,7 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E4" s="72">
+      <c r="E4" s="99">
         <v>0.58778127</v>
       </c>
       <c r="F4" t="inlineStr">
@@ -1367,7 +1719,7 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E5" s="72">
+      <c r="E5" s="99">
         <v>0.34748912</v>
       </c>
       <c r="F5" t="inlineStr">
@@ -1395,7 +1747,7 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E6" s="72">
+      <c r="E6" s="99">
         <v>0.22603208</v>
       </c>
       <c r="F6" t="inlineStr">
@@ -1423,7 +1775,7 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E7" s="72">
+      <c r="E7" s="99">
         <v>0.2319889</v>
       </c>
       <c r="F7" t="inlineStr">
@@ -1444,41 +1796,41 @@
   <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="44.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="45.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="34.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="101" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="101" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="101" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="101" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="101" t="inlineStr">
         <is>
           <t>Personas dadas por desaparecidas</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="101" t="inlineStr">
         <is>
           <t>Proporción dentro de la provincia</t>
         </is>
@@ -1503,10 +1855,10 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E2" s="73">
+      <c r="E2" s="103">
         <v>738</v>
       </c>
-      <c r="F2" s="75">
+      <c r="F2" s="105">
         <v>0.651943462897526</v>
       </c>
     </row>
@@ -1529,10 +1881,10 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E3" s="73">
+      <c r="E3" s="103">
         <v>145</v>
       </c>
-      <c r="F3" s="75">
+      <c r="F3" s="105">
         <v>0.128091872791519</v>
       </c>
     </row>
@@ -1555,10 +1907,10 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E4" s="73">
+      <c r="E4" s="103">
         <v>97</v>
       </c>
-      <c r="F4" s="75">
+      <c r="F4" s="105">
         <v>0.0856890459363958</v>
       </c>
     </row>
@@ -1581,10 +1933,10 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E5" s="73">
+      <c r="E5" s="103">
         <v>71</v>
       </c>
-      <c r="F5" s="75">
+      <c r="F5" s="105">
         <v>0.0627208480565371</v>
       </c>
     </row>
@@ -1607,10 +1959,10 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E6" s="73">
+      <c r="E6" s="103">
         <v>62</v>
       </c>
-      <c r="F6" s="75">
+      <c r="F6" s="105">
         <v>0.0547703180212014</v>
       </c>
     </row>
@@ -1633,38 +1985,38 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E7" s="73">
+      <c r="E7" s="103">
         <v>19</v>
       </c>
-      <c r="F7" s="75">
+      <c r="F7" s="105">
         <v>0.0167844522968198</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="102" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="102" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="102" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="102" t="inlineStr">
         <is>
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E8" s="74">
+      <c r="E8" s="104">
         <v>1132</v>
       </c>
-      <c r="F8" s="76">
+      <c r="F8" s="106">
         <v>1</v>
       </c>
     </row>
@@ -1677,299 +2029,264 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="6.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="45.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="44.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="63.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="62.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>periodo</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>ambito</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>valor</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>n_resp</t>
+      <c r="A1" s="108" t="inlineStr">
+        <is>
+          <t>Código DANE</t>
+        </is>
+      </c>
+      <c r="B1" s="108" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C1" s="108" t="inlineStr">
+        <is>
+          <t>Subregión</t>
+        </is>
+      </c>
+      <c r="D1" s="108" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="E1" s="108" t="inlineStr">
+        <is>
+          <t>Sujetos de reparación colectiva reconocidos</t>
+        </is>
+      </c>
+      <c r="F1" s="108" t="inlineStr">
+        <is>
+          <t>Sujetos con Plan Integral de Reparación Colectiva implementado</t>
+        </is>
+      </c>
+      <c r="G1" s="108" t="inlineStr">
+        <is>
+          <t>% de avance del PIRC, promedio (solo sujetos con plan activo)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2">
-        <v>2018</v>
+        <v>5234</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>En su barrio o vereda</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>0.107597436115821</v>
-      </c>
-      <c r="D2">
-        <v>192</v>
+          <t>Dabeiba</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="E2" s="110">
+        <v>2</v>
+      </c>
+      <c r="F2" s="112">
+        <v>0</v>
+      </c>
+      <c r="G2" s="114">
+        <v>0.5114898989895</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2019 (1)</t>
-        </is>
+      <c r="A3">
+        <v>5284</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>En su barrio o vereda</t>
-        </is>
-      </c>
-      <c r="C3">
-        <v>0.10428931790765</v>
-      </c>
-      <c r="D3">
-        <v>192</v>
+          <t>Frontino</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="E3" s="110">
+        <v>1</v>
+      </c>
+      <c r="F3" s="112">
+        <v>0</v>
+      </c>
+      <c r="G3" s="114" t="e">
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2019 (2)</t>
-        </is>
+      <c r="A4">
+        <v>5842</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>En su barrio o vereda</t>
-        </is>
-      </c>
-      <c r="C4">
-        <v>0.0643880184796319</v>
-      </c>
-      <c r="D4">
-        <v>192</v>
+          <t>Uramita</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="E4" s="110">
+        <v>1</v>
+      </c>
+      <c r="F4" s="112">
+        <v>0</v>
+      </c>
+      <c r="G4" s="114" t="e">
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>2021</v>
+        <v>5004</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>En su barrio o vereda</t>
-        </is>
-      </c>
-      <c r="C5">
-        <v>0.105853262928549</v>
-      </c>
-      <c r="D5">
-        <v>216</v>
+          <t>Abriaquí</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="E5" s="110">
+        <v>0</v>
+      </c>
+      <c r="F5" s="112">
+        <v>0</v>
+      </c>
+      <c r="G5" s="114" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>2022</v>
+        <v>5138</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>En su barrio o vereda</t>
-        </is>
-      </c>
-      <c r="C6">
-        <v>0.120374203899533</v>
-      </c>
-      <c r="D6">
-        <v>216</v>
+          <t>Cañasgordas</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="E6" s="110">
+        <v>0</v>
+      </c>
+      <c r="F6" s="112">
+        <v>0</v>
+      </c>
+      <c r="G6" s="114" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>2023</v>
+        <v>5543</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>En su barrio o vereda</t>
-        </is>
-      </c>
-      <c r="C7">
-        <v>0.119087878401574</v>
-      </c>
-      <c r="D7">
-        <v>216</v>
+          <t>Peque</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="E7" s="110">
+        <v>0</v>
+      </c>
+      <c r="F7" s="112">
+        <v>0</v>
+      </c>
+      <c r="G7" s="114" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>2024</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>En su barrio o vereda</t>
-        </is>
-      </c>
-      <c r="C8">
-        <v>0.0584990995873746</v>
-      </c>
-      <c r="D8">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9">
-        <v>2025</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>En su barrio o vereda</t>
-        </is>
-      </c>
-      <c r="C9">
-        <v>0.0832542581004119</v>
-      </c>
-      <c r="D9">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10">
-        <v>2018</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>En su municipio</t>
-        </is>
-      </c>
-      <c r="C10">
-        <v>0.159936197463361</v>
-      </c>
-      <c r="D10">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2019 (1)</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>En su municipio</t>
-        </is>
-      </c>
-      <c r="C11">
-        <v>0.130042120529851</v>
-      </c>
-      <c r="D11">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2019 (2)</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>En su municipio</t>
-        </is>
-      </c>
-      <c r="C12">
-        <v>0.101814797815791</v>
-      </c>
-      <c r="D12">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13">
-        <v>2021</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>En su municipio</t>
-        </is>
-      </c>
-      <c r="C13">
-        <v>0.120805081792468</v>
-      </c>
-      <c r="D13">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14">
-        <v>2022</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>En su municipio</t>
-        </is>
-      </c>
-      <c r="C14">
-        <v>0.177710895096566</v>
-      </c>
-      <c r="D14">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15">
-        <v>2023</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>En su municipio</t>
-        </is>
-      </c>
-      <c r="C15">
-        <v>0.141604789747684</v>
-      </c>
-      <c r="D15">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16">
-        <v>2024</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>En su municipio</t>
-        </is>
-      </c>
-      <c r="C16">
-        <v>0.0726778451289176</v>
-      </c>
-      <c r="D16">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17">
-        <v>2025</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>En su municipio</t>
-        </is>
-      </c>
-      <c r="C17">
-        <v>0.108870518255134</v>
-      </c>
-      <c r="D17">
-        <v>216</v>
+      <c r="A8" s="109" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B8" s="109" t="inlineStr">
+        <is>
+          <t>TOTAL PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="C8" s="109" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D8" s="109" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E8" s="111">
+        <v>4</v>
+      </c>
+      <c r="F8" s="113">
+        <v>0</v>
+      </c>
+      <c r="G8" s="115">
+        <v>0.5114898989895</v>
       </c>
     </row>
   </sheetData>
@@ -1981,131 +2298,266 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="43.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="42.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="47.711"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
+    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>municipio</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>n_solicitudes</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>pob</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>tasa_solicitudes</t>
+      <c r="A1" s="117" t="inlineStr">
+        <is>
+          <t>Código DANE</t>
+        </is>
+      </c>
+      <c r="B1" s="117" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C1" s="117" t="inlineStr">
+        <is>
+          <t>Subregión</t>
+        </is>
+      </c>
+      <c r="D1" s="117" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="E1" s="117" t="inlineStr">
+        <is>
+          <t>Sujeto de reparación colectiva</t>
+        </is>
+      </c>
+      <c r="F1" s="117" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="G1" s="117" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="H1" s="117" t="inlineStr">
+        <is>
+          <t>Fase del Plan Integral de Reparación Colectiva</t>
+        </is>
+      </c>
+      <c r="I1" s="117" t="inlineStr">
+        <is>
+          <t>% de avance del PIRC</t>
+        </is>
+      </c>
+      <c r="J1" s="117" t="inlineStr">
+        <is>
+          <t>Zona PDET</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Abriaquí</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>20</v>
-      </c>
-      <c r="C2">
-        <v>2807</v>
-      </c>
-      <c r="D2">
-        <v>7.12504453152832</v>
+      <c r="A2">
+        <v>5234</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dabeiba</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>CENTRO POBLADO LA BALSITA</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>No Étnico</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>COMUNIDAD CAMPESINA</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>IMPLEMENTACIÓN</t>
+        </is>
+      </c>
+      <c r="I2" s="118">
+        <v>0.95909090909</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>PDET Urabá Antioqueño</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Cañasgordas</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>141</v>
-      </c>
-      <c r="C3">
-        <v>15470</v>
-      </c>
-      <c r="D3">
-        <v>9.11441499676794</v>
+      <c r="A3">
+        <v>5234</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dabeiba</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>COMUNIDAD CHOROMANDO</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Étnico</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>COMUNIDAD INDÍGENA (Decreto 4633 de 2011)</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTACIÓN</t>
+        </is>
+      </c>
+      <c r="I3" s="118">
+        <v>0.063888888889</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>PDET Urabá Antioqueño</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Dabeiba</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>677</v>
-      </c>
-      <c r="C4">
-        <v>24808</v>
-      </c>
-      <c r="D4">
-        <v>27.2895840051596</v>
+      <c r="A4">
+        <v>5284</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Frontino</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>CABILDO MAYOR FRONTINO</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Étnico</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>COMUNIDAD INDÍGENA (Decreto 4633 de 2011)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>ALISTAMIENTO</t>
+        </is>
+      </c>
+      <c r="I4" s="118" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>No PDET</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Frontino</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>212</v>
-      </c>
-      <c r="C5">
-        <v>21778</v>
-      </c>
-      <c r="D5">
-        <v>9.73459454495362</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Peque</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>54</v>
-      </c>
-      <c r="C6">
-        <v>8782</v>
-      </c>
-      <c r="D6">
-        <v>6.14894101571396</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A5">
+        <v>5842</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>Uramita</t>
         </is>
       </c>
-      <c r="B7">
-        <v>49</v>
-      </c>
-      <c r="C7">
-        <v>7455</v>
-      </c>
-      <c r="D7">
-        <v>6.57276995305164</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>RESGUARDO INDIGENA SANTA MARIA DEL CHARCÓN</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Étnico</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>COMUNIDAD INDÍGENA (Decreto 4633 de 2011)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>IDENTIFICACIÓN</t>
+        </is>
+      </c>
+      <c r="I5" s="118" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>No PDET</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2117,107 +2569,299 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="7.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>municipio</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>desaparecidos</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>prop_desaparecidos</t>
+      <c r="A1" s="120" t="inlineStr">
+        <is>
+          <t>periodo</t>
+        </is>
+      </c>
+      <c r="B1" s="120" t="inlineStr">
+        <is>
+          <t>ambito</t>
+        </is>
+      </c>
+      <c r="C1" s="120" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+      <c r="D1" s="120" t="inlineStr">
+        <is>
+          <t>n_resp</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Dabeiba</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>738</v>
+      <c r="A2">
+        <v>2018</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>En su barrio o vereda</t>
+        </is>
       </c>
       <c r="C2">
-        <v>0.651943462897526</v>
+        <v>0.107597436115821</v>
+      </c>
+      <c r="D2">
+        <v>192</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Frontino</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>145</v>
+          <t>2019 (1)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>En su barrio o vereda</t>
+        </is>
       </c>
       <c r="C3">
-        <v>0.128091872791519</v>
+        <v>0.10428931790765</v>
+      </c>
+      <c r="D3">
+        <v>192</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Peque</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>97</v>
+          <t>2019 (2)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>En su barrio o vereda</t>
+        </is>
       </c>
       <c r="C4">
-        <v>0.0856890459363958</v>
+        <v>0.0643880184796319</v>
+      </c>
+      <c r="D4">
+        <v>192</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Cañasgordas</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>71</v>
+      <c r="A5">
+        <v>2021</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>En su barrio o vereda</t>
+        </is>
       </c>
       <c r="C5">
-        <v>0.0627208480565371</v>
+        <v>0.105853262928549</v>
+      </c>
+      <c r="D5">
+        <v>216</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Uramita</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>62</v>
+      <c r="A6">
+        <v>2022</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>En su barrio o vereda</t>
+        </is>
       </c>
       <c r="C6">
-        <v>0.0547703180212014</v>
+        <v>0.120374203899533</v>
+      </c>
+      <c r="D6">
+        <v>216</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Abriaquí</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>19</v>
+      <c r="A7">
+        <v>2023</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>En su barrio o vereda</t>
+        </is>
       </c>
       <c r="C7">
-        <v>0.0167844522968198</v>
+        <v>0.119087878401574</v>
+      </c>
+      <c r="D7">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>2024</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>En su barrio o vereda</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>0.0584990995873746</v>
+      </c>
+      <c r="D8">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>2025</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>En su barrio o vereda</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>0.0832542581004119</v>
+      </c>
+      <c r="D9">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>2018</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>En su municipio</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>0.159936197463361</v>
+      </c>
+      <c r="D10">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2019 (1)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>En su municipio</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>0.130042120529851</v>
+      </c>
+      <c r="D11">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2019 (2)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>En su municipio</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>0.101814797815791</v>
+      </c>
+      <c r="D12">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>2021</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>En su municipio</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>0.120805081792468</v>
+      </c>
+      <c r="D13">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>2022</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>En su municipio</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>0.177710895096566</v>
+      </c>
+      <c r="D14">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>2023</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>En su municipio</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>0.141604789747684</v>
+      </c>
+      <c r="D15">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>2024</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>En su municipio</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>0.0726778451289176</v>
+      </c>
+      <c r="D16">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>2025</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>En su municipio</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>0.108870518255134</v>
+      </c>
+      <c r="D17">
+        <v>216</v>
       </c>
     </row>
   </sheetData>
@@ -2229,22 +2873,34 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="6.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="122" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>victimas_ocurrencia</t>
+      <c r="B1" s="122" t="inlineStr">
+        <is>
+          <t>n_solicitudes</t>
+        </is>
+      </c>
+      <c r="C1" s="122" t="inlineStr">
+        <is>
+          <t>pob</t>
+        </is>
+      </c>
+      <c r="D1" s="122" t="inlineStr">
+        <is>
+          <t>tasa_solicitudes</t>
         </is>
       </c>
     </row>
@@ -2255,7 +2911,13 @@
         </is>
       </c>
       <c r="B2">
-        <v>2644</v>
+        <v>20</v>
+      </c>
+      <c r="C2">
+        <v>2807</v>
+      </c>
+      <c r="D2">
+        <v>7.12504453152832</v>
       </c>
     </row>
     <row r="3">
@@ -2265,7 +2927,13 @@
         </is>
       </c>
       <c r="B3">
-        <v>13875</v>
+        <v>141</v>
+      </c>
+      <c r="C3">
+        <v>15470</v>
+      </c>
+      <c r="D3">
+        <v>9.11441499676794</v>
       </c>
     </row>
     <row r="4">
@@ -2275,7 +2943,13 @@
         </is>
       </c>
       <c r="B4">
-        <v>55034</v>
+        <v>677</v>
+      </c>
+      <c r="C4">
+        <v>24808</v>
+      </c>
+      <c r="D4">
+        <v>27.2895840051596</v>
       </c>
     </row>
     <row r="5">
@@ -2285,7 +2959,13 @@
         </is>
       </c>
       <c r="B5">
-        <v>22256</v>
+        <v>212</v>
+      </c>
+      <c r="C5">
+        <v>21778</v>
+      </c>
+      <c r="D5">
+        <v>9.73459454495362</v>
       </c>
     </row>
     <row r="6">
@@ -2295,7 +2975,13 @@
         </is>
       </c>
       <c r="B6">
-        <v>19417</v>
+        <v>54</v>
+      </c>
+      <c r="C6">
+        <v>8782</v>
+      </c>
+      <c r="D6">
+        <v>6.14894101571396</v>
       </c>
     </row>
     <row r="7">
@@ -2305,7 +2991,13 @@
         </is>
       </c>
       <c r="B7">
-        <v>9441</v>
+        <v>49</v>
+      </c>
+      <c r="C7">
+        <v>7455</v>
+      </c>
+      <c r="D7">
+        <v>6.57276995305164</v>
       </c>
     </row>
   </sheetData>
@@ -2317,237 +3009,107 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>hecho</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>victimas_ocurrencia</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>proporcion_pct</t>
+      <c r="A1" s="124" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="B1" s="124" t="inlineStr">
+        <is>
+          <t>desaparecidos</t>
+        </is>
+      </c>
+      <c r="C1" s="124" t="inlineStr">
+        <is>
+          <t>prop_desaparecidos</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Desplazamiento forzado</t>
+          <t>Dabeiba</t>
         </is>
       </c>
       <c r="B2">
-        <v>97659</v>
+        <v>738</v>
       </c>
       <c r="C2">
-        <v>0.796130988774487</v>
+        <v>0.651943462897526</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Homicidio</t>
+          <t>Frontino</t>
         </is>
       </c>
       <c r="B3">
-        <v>10715</v>
+        <v>145</v>
       </c>
       <c r="C3">
-        <v>0.0873503061132986</v>
+        <v>0.128091872791519</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Amenaza</t>
+          <t>Peque</t>
         </is>
       </c>
       <c r="B4">
-        <v>6343</v>
+        <v>97</v>
       </c>
       <c r="C4">
-        <v>0.0517090986165798</v>
+        <v>0.0856890459363958</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Desaparición forzada</t>
+          <t>Cañasgordas</t>
         </is>
       </c>
       <c r="B5">
-        <v>2445</v>
+        <v>71</v>
       </c>
       <c r="C5">
-        <v>0.0199320110543178</v>
+        <v>0.0627208480565371</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sin información</t>
+          <t>Uramita</t>
         </is>
       </c>
       <c r="B6">
-        <v>1771</v>
+        <v>62</v>
       </c>
       <c r="C6">
-        <v>0.0144374607677697</v>
+        <v>0.0547703180212014</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Confinamiento</t>
+          <t>Abriaquí</t>
         </is>
       </c>
       <c r="B7">
-        <v>1097</v>
+        <v>19</v>
       </c>
       <c r="C7">
-        <v>0.00894291048122152</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Pérdida de bienes muebles/inmuebles</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>909</v>
-      </c>
-      <c r="C8">
-        <v>0.00741030595025557</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Secuestro</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>536</v>
-      </c>
-      <c r="C9">
-        <v>0.00436955334360504</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Acto terrorista/atentados/combates</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>289</v>
-      </c>
-      <c r="C10">
-        <v>0.00235597185877212</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Delitos contra libertad/integridad sexual</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>231</v>
-      </c>
-      <c r="C11">
-        <v>0.00188314705666561</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Minas antipersonal/MUSE</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>165</v>
-      </c>
-      <c r="C12">
-        <v>0.00134510504047543</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Lesiones personales físicas</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>162</v>
-      </c>
-      <c r="C13">
-        <v>0.00132064858519406</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Vinculación de NNA a grupos armados</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>115</v>
-      </c>
-      <c r="C14">
-        <v>0.000937497452452575</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Lesiones personales psicológicas</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>111</v>
-      </c>
-      <c r="C15">
-        <v>0.000904888845410746</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Tortura</t>
-        </is>
-      </c>
-      <c r="B16">
-        <v>82</v>
-      </c>
-      <c r="C16">
-        <v>0.000668476444357488</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Abandono o despojo de tierras</t>
-        </is>
-      </c>
-      <c r="B17">
-        <v>37</v>
-      </c>
-      <c r="C17">
-        <v>0.000301629615136915</v>
+        <v>0.0167844522968198</v>
       </c>
     </row>
   </sheetData>
@@ -2559,106 +3121,83 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Código DANE</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Municipio</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Homicidios por 100.000 hab.</t>
+      <c r="A1" s="126" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="B1" s="126" t="inlineStr">
+        <is>
+          <t>victimas_ocurrencia</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>5004</v>
-      </c>
-      <c r="B2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Abriaquí</t>
         </is>
       </c>
-      <c r="C2">
-        <v>0</v>
+      <c r="B2">
+        <v>2644</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>5138</v>
-      </c>
-      <c r="B3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Cañasgordas</t>
         </is>
       </c>
-      <c r="C3">
-        <v>38.7847446670976</v>
+      <c r="B3">
+        <v>13875</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>5234</v>
-      </c>
-      <c r="B4" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Dabeiba</t>
         </is>
       </c>
-      <c r="C4">
-        <v>52.4024508223154</v>
+      <c r="B4">
+        <v>55034</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>5284</v>
-      </c>
-      <c r="B5" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Frontino</t>
         </is>
       </c>
-      <c r="C5">
-        <v>32.1425291578657</v>
+      <c r="B5">
+        <v>22256</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5543</v>
-      </c>
-      <c r="B6" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Peque</t>
         </is>
       </c>
-      <c r="C6">
-        <v>11.3869278068777</v>
+      <c r="B6">
+        <v>19417</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>5842</v>
-      </c>
-      <c r="B7" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Uramita</t>
         </is>
       </c>
-      <c r="C7">
-        <v>13.4138162307176</v>
+      <c r="B7">
+        <v>9441</v>
       </c>
     </row>
   </sheetData>
@@ -2673,59 +3212,59 @@
   <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="44.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="45.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="11" t="inlineStr">
         <is>
           <t>Año</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>Hectáreas con permisos</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="11" t="inlineStr">
         <is>
           <t>Hectáreas en tránsito</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="11" t="inlineStr">
         <is>
           <t>Hectáreas ilícita</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="11" t="inlineStr">
         <is>
           <t>Total EVOA (ha)</t>
         </is>
@@ -2750,19 +3289,19 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E2" s="10">
+      <c r="E2" s="13">
         <v>2018</v>
       </c>
-      <c r="F2" s="12">
+      <c r="F2" s="15">
         <v>0</v>
       </c>
-      <c r="G2" s="14">
+      <c r="G2" s="17">
         <v>0</v>
       </c>
-      <c r="H2" s="16">
+      <c r="H2" s="19">
         <v>7.8075</v>
       </c>
-      <c r="I2" s="18">
+      <c r="I2" s="21">
         <v>7.8075</v>
       </c>
     </row>
@@ -2785,19 +3324,19 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E3" s="10">
+      <c r="E3" s="13">
         <v>2018</v>
       </c>
-      <c r="F3" s="12">
+      <c r="F3" s="15">
         <v>0</v>
       </c>
-      <c r="G3" s="14">
+      <c r="G3" s="17">
         <v>0</v>
       </c>
-      <c r="H3" s="16">
+      <c r="H3" s="19">
         <v>14.314907</v>
       </c>
-      <c r="I3" s="18">
+      <c r="I3" s="21">
         <v>14.314907</v>
       </c>
     </row>
@@ -2820,19 +3359,19 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E4" s="10">
+      <c r="E4" s="13">
         <v>2019</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="15">
         <v>0</v>
       </c>
-      <c r="G4" s="14">
+      <c r="G4" s="17">
         <v>0</v>
       </c>
-      <c r="H4" s="16">
+      <c r="H4" s="19">
         <v>4.5</v>
       </c>
-      <c r="I4" s="18">
+      <c r="I4" s="21">
         <v>4.5</v>
       </c>
     </row>
@@ -2855,19 +3394,19 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="13">
         <v>2020</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="15">
         <v>0</v>
       </c>
-      <c r="G5" s="14">
+      <c r="G5" s="17">
         <v>0</v>
       </c>
-      <c r="H5" s="16">
+      <c r="H5" s="19">
         <v>6.66</v>
       </c>
-      <c r="I5" s="18">
+      <c r="I5" s="21">
         <v>6.66</v>
       </c>
     </row>
@@ -2890,352 +3429,352 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="13">
         <v>2020</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="15">
         <v>8.505001</v>
       </c>
-      <c r="G6" s="14">
+      <c r="G6" s="17">
         <v>0</v>
       </c>
-      <c r="H6" s="16">
+      <c r="H6" s="19">
         <v>0</v>
       </c>
-      <c r="I6" s="18">
+      <c r="I6" s="21">
         <v>8.505001</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="14">
         <v>2018</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="16">
         <v>0</v>
       </c>
-      <c r="G7" s="15">
+      <c r="G7" s="18">
         <v>0</v>
       </c>
-      <c r="H7" s="17">
+      <c r="H7" s="20">
         <v>22.122407</v>
       </c>
-      <c r="I7" s="19">
+      <c r="I7" s="22">
         <v>22.122407</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="14">
         <v>2019</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="16">
         <v>0</v>
       </c>
-      <c r="G8" s="15">
+      <c r="G8" s="18">
         <v>0</v>
       </c>
-      <c r="H8" s="17">
+      <c r="H8" s="20">
         <v>4.5</v>
       </c>
-      <c r="I8" s="19">
+      <c r="I8" s="22">
         <v>4.5</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="14">
         <v>2020</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="16">
         <v>8.505001</v>
       </c>
-      <c r="G9" s="15">
+      <c r="G9" s="18">
         <v>0</v>
       </c>
-      <c r="H9" s="17">
+      <c r="H9" s="20">
         <v>6.66</v>
       </c>
-      <c r="I9" s="19">
+      <c r="I9" s="22">
         <v>15.165001</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>TOTAL SUBREGIÓN OCCIDENTE</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="14">
         <v>2018</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="16">
         <v>0</v>
       </c>
-      <c r="G10" s="15">
+      <c r="G10" s="18">
         <v>0</v>
       </c>
-      <c r="H10" s="17">
+      <c r="H10" s="20">
         <v>22.122407</v>
       </c>
-      <c r="I10" s="19">
+      <c r="I10" s="22">
         <v>22.122407</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>TOTAL SUBREGIÓN OCCIDENTE</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="14">
         <v>2019</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="16">
         <v>0</v>
       </c>
-      <c r="G11" s="15">
+      <c r="G11" s="18">
         <v>0</v>
       </c>
-      <c r="H11" s="17">
+      <c r="H11" s="20">
         <v>4.5</v>
       </c>
-      <c r="I11" s="19">
+      <c r="I11" s="22">
         <v>4.5</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>TOTAL SUBREGIÓN OCCIDENTE</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E12" s="11">
+      <c r="E12" s="14">
         <v>2020</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="16">
         <v>8.505001</v>
       </c>
-      <c r="G12" s="15">
+      <c r="G12" s="18">
         <v>0</v>
       </c>
-      <c r="H12" s="17">
+      <c r="H12" s="20">
         <v>6.66</v>
       </c>
-      <c r="I12" s="19">
+      <c r="I12" s="22">
         <v>15.165001</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>TOTAL DEPARTAMENTO (ANTIOQUIA)</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t>DEPARTAMENTO DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E13" s="11">
+      <c r="E13" s="14">
         <v>2018</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="16">
         <v>16186.547037</v>
       </c>
-      <c r="G13" s="15">
+      <c r="G13" s="18">
         <v>1633.054856</v>
       </c>
-      <c r="H13" s="17">
+      <c r="H13" s="20">
         <v>18627.422655</v>
       </c>
-      <c r="I13" s="19">
+      <c r="I13" s="22">
         <v>36447.024548</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>TOTAL DEPARTAMENTO (ANTIOQUIA)</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>DEPARTAMENTO DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E14" s="11">
+      <c r="E14" s="14">
         <v>2019</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="16">
         <v>17799.238713</v>
       </c>
-      <c r="G14" s="15">
+      <c r="G14" s="18">
         <v>1658.203768</v>
       </c>
-      <c r="H14" s="17">
+      <c r="H14" s="20">
         <v>20744.042756</v>
       </c>
-      <c r="I14" s="19">
+      <c r="I14" s="22">
         <v>40201.485237</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>TOTAL DEPARTAMENTO (ANTIOQUIA)</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t>DEPARTAMENTO DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E15" s="11">
+      <c r="E15" s="14">
         <v>2020</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="16">
         <v>19240.998973</v>
       </c>
-      <c r="G15" s="15">
+      <c r="G15" s="18">
         <v>1806.249069</v>
       </c>
-      <c r="H15" s="17">
+      <c r="H15" s="20">
         <v>19842.333019</v>
       </c>
-      <c r="I15" s="19">
+      <c r="I15" s="22">
         <v>40889.581061</v>
       </c>
     </row>
@@ -3248,25 +3787,616 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="42.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="128" t="inlineStr">
+        <is>
+          <t>hecho</t>
+        </is>
+      </c>
+      <c r="B1" s="128" t="inlineStr">
+        <is>
+          <t>victimas_ocurrencia</t>
+        </is>
+      </c>
+      <c r="C1" s="128" t="inlineStr">
+        <is>
+          <t>proporcion_pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Desplazamiento forzado</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>97659</v>
+      </c>
+      <c r="C2">
+        <v>0.796130988774487</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Homicidio</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>10715</v>
+      </c>
+      <c r="C3">
+        <v>0.0873503061132986</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Amenaza</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>6343</v>
+      </c>
+      <c r="C4">
+        <v>0.0517090986165798</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Desaparición forzada</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>2445</v>
+      </c>
+      <c r="C5">
+        <v>0.0199320110543178</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Sin información</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>1771</v>
+      </c>
+      <c r="C6">
+        <v>0.0144374607677697</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Confinamiento</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>1097</v>
+      </c>
+      <c r="C7">
+        <v>0.00894291048122152</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Pérdida de bienes muebles/inmuebles</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>909</v>
+      </c>
+      <c r="C8">
+        <v>0.00741030595025557</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Secuestro</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>536</v>
+      </c>
+      <c r="C9">
+        <v>0.00436955334360504</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Acto terrorista/atentados/combates</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>289</v>
+      </c>
+      <c r="C10">
+        <v>0.00235597185877212</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Delitos contra libertad/integridad sexual</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>231</v>
+      </c>
+      <c r="C11">
+        <v>0.00188314705666561</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Minas antipersonal/MUSE</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>165</v>
+      </c>
+      <c r="C12">
+        <v>0.00134510504047543</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Lesiones personales físicas</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>162</v>
+      </c>
+      <c r="C13">
+        <v>0.00132064858519406</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Vinculación de NNA a grupos armados</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>115</v>
+      </c>
+      <c r="C14">
+        <v>0.000937497452452575</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Lesiones personales psicológicas</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>111</v>
+      </c>
+      <c r="C15">
+        <v>0.000904888845410746</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Tortura</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>82</v>
+      </c>
+      <c r="C16">
+        <v>0.000668476444357488</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Abandono o despojo de tierras</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>37</v>
+      </c>
+      <c r="C17">
+        <v>0.000301629615136915</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="2.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="130" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="B1" s="130" t="inlineStr">
+        <is>
+          <t>estado_fase</t>
+        </is>
+      </c>
+      <c r="C1" s="130" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Dabeiba</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ALISTAMIENTO</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Dabeiba</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CARACTERIZACIÓN DEL DAÑO</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Dabeiba</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DIAGNÓSTICO DEL DAÑO</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Dabeiba</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>DISEÑO Y FORMULACIÓN</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Dabeiba</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>IDENTIFICACIÓN</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Dabeiba</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>IMPLEMENTACIÓN</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Dabeiba</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>IMPLEMENTADO</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Frontino</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ALISTAMIENTO</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Frontino</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CARACTERIZACIÓN DEL DAÑO</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Frontino</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>DIAGNÓSTICO DEL DAÑO</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Frontino</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>DISEÑO Y FORMULACIÓN</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Frontino</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>IDENTIFICACIÓN</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Frontino</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>IMPLEMENTACIÓN</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Frontino</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>IMPLEMENTADO</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Uramita</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ALISTAMIENTO</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Uramita</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CARACTERIZACIÓN DEL DAÑO</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Uramita</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>DIAGNÓSTICO DEL DAÑO</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Uramita</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>DISEÑO Y FORMULACIÓN</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Uramita</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>IDENTIFICACIÓN</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Uramita</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>IMPLEMENTACIÓN</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Uramita</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>IMPLEMENTADO</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
+    <col min="1" max="2" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="28.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="132" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="132" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="132" t="inlineStr">
         <is>
           <t>Homicidios por 100.000 hab.</t>
         </is>
@@ -3348,6 +4478,1210 @@
       </c>
       <c r="C7">
         <v>13.4138162307176</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:C91"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="28.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="134" t="inlineStr">
+        <is>
+          <t>Código DANE</t>
+        </is>
+      </c>
+      <c r="B1" s="134" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C1" s="134" t="inlineStr">
+        <is>
+          <t>Homicidios por 100.000 hab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>5001</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>13.1706813513831</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>5002</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Abejorral</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>28.3728188395517</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>5004</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Abriaquí</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>5021</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Alejandría</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>18.9214758751183</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>5030</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Amagá</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>36.5207864142675</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>5031</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Amalfi</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>113.581606663454</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>5034</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Andes</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>147.684440231887</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>5036</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Angelópolis</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>48.363694986297</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>5038</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>55.9507633282711</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>5040</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>218.683147135726</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>5042</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Santa Fe de Antioquia</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>31.6667253087506</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>5044</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Anzá</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>52.0765525322224</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>5055</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Argelia</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>12.1728545343883</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>5079</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Barbosa</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>17.3351193759357</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>5086</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Belmira</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>81.2875955129247</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>5088</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Bello</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>7.64226237548096</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>5091</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Betania</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>176.727746256162</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>5093</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Betulia</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>206.124852767962</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>5101</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ciudad Bolívar</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>137.815979400138</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>5107</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>226.21591051904</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>5113</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Buriticá</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>90.7852927825692</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>5125</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Caicedo</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>32.9416932030306</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>5129</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>12.3495599065924</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>5134</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Campamento</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>99.9500249875062</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>5138</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Cañasgordas</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>38.7847446670976</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>5145</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Caramanta</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>22.2271615914648</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>5150</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>76.103500761035</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>5197</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Cocorná</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>24.8617067561688</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>5206</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Concepción</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>39.1236306729264</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>5209</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Concordia</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>99.2645399990976</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>5212</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Copacabana</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>16.5049184657028</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>5234</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Dabeiba</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>52.4024508223154</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>5237</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Donmatías</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>25.2614560703279</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>5240</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Ebéjico</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>5264</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Entrerríos</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>15.7035175879397</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>5266</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>3.02300887630981</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>5282</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Fredonia</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>22.7264118783379</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>5284</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Frontino</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>32.1425291578657</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>5306</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Giraldo</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>15.6152404747033</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>5308</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Girardota</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>4.88289197415322</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>5310</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Gómez Plata</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>57.8424756579582</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>5313</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>19.0276852820854</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>5315</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>42.8021115708375</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>5321</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Guatapé</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>30.9437854564208</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>5347</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Heliconia</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>39.6982929734021</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>5353</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Hispania</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>168.662506324844</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>5360</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Itagüí</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>3.61215918457148</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>5361</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>71.15026257835</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>5364</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Jardín</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>71.2758374910905</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>5368</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Jericó</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>69.5603784084585</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>5380</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>La Estrella</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>9.62822997027284</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>5390</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>La Pintada</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>80.887450889762</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>5400</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>70.6655027642682</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>5440</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Marinilla</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>33.6066675628445</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>5467</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Montebello</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>45.8855919241358</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>5483</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>63.6363636363636</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>5501</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Olaya</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>5541</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Peñol</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>41.9691946111554</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>5543</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Peque</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>11.3869278068777</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>5576</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Pueblorrico</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>99.41455870982</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>5604</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Remedios</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>118.106659398565</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>5628</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>80.7346856393178</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>5631</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Sabaneta</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>2.81288677193114</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>5642</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Salgar</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>100.396301188904</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>5647</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>San Andrés de Cuerquía</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>391.786003782761</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>5649</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>11.8077695123391</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>5652</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>33.0141961043249</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>5656</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>San Jerónimo</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>81.7661488143908</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>5658</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>San José de la Montaña</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>74.6825989544436</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>5660</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>San Luis</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>62.2966705890496</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>5664</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>San Pedro de los Milagros</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>31.4084443846188</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>5667</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>San Rafael</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>22.9739819654242</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>5674</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>San Vicente Ferrer</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>40.3616402970617</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>5679</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Santa Bárbara</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>33.9328130302002</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>5686</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Santa Rosa de Osos</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>22.3541392414495</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>5736</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>66.0854535749689</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>5756</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Sonsón</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>38.9105058365759</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>5789</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Támesis</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>5.99736116108912</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>5792</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Tarso</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>76.2660158633313</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>5809</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Titiribí</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>60.6743520845974</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>5819</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>124.378109452736</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>5842</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Uramita</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>13.4138162307176</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>5847</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Urrao</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>96.9113417531574</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>5854</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>126.548554682297</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>5856</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>14.8942508191838</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>5858</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Vegachí</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>41.1184210526316</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>5861</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Venecia</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>40.2835965194973</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>5885</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Yalí</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>25.9100919808265</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>5887</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>59.6886639289466</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>5890</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Yolombó</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>31.9514338205927</v>
       </c>
     </row>
   </sheetData>
@@ -3362,47 +5696,47 @@
   <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="44.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="45.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="28.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="34.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="24" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="24" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="24" t="inlineStr">
         <is>
           <t>Hurtos por 100.000 hab.</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="24" t="inlineStr">
         <is>
           <t>Homicidios por 100.000 hab.</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="24" t="inlineStr">
         <is>
           <t>Violencia intrafamiliar por 100.000 hab.</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="24" t="inlineStr">
         <is>
           <t>Delitos sexuales por 100.000 hab.</t>
         </is>
@@ -3422,16 +5756,16 @@
           <t>OCCIDENTE</t>
         </is>
       </c>
-      <c r="D2" s="20">
+      <c r="D2" s="26">
         <v>0</v>
       </c>
-      <c r="E2" s="22">
+      <c r="E2" s="28">
         <v>0</v>
       </c>
-      <c r="F2" s="24">
+      <c r="F2" s="30">
         <v>0</v>
       </c>
-      <c r="G2" s="26">
+      <c r="G2" s="32">
         <v>0</v>
       </c>
     </row>
@@ -3449,16 +5783,16 @@
           <t>OCCIDENTE</t>
         </is>
       </c>
-      <c r="D3" s="20">
+      <c r="D3" s="26">
         <v>32.3206205559147</v>
       </c>
-      <c r="E3" s="22">
+      <c r="E3" s="28">
         <v>38.7847446670976</v>
       </c>
-      <c r="F3" s="24">
+      <c r="F3" s="30">
         <v>64.6412411118293</v>
       </c>
-      <c r="G3" s="26">
+      <c r="G3" s="32">
         <v>38.7847446670976</v>
       </c>
     </row>
@@ -3476,16 +5810,16 @@
           <t>OCCIDENTE</t>
         </is>
       </c>
-      <c r="D4" s="20">
+      <c r="D4" s="26">
         <v>64.4953240890035</v>
       </c>
-      <c r="E4" s="22">
+      <c r="E4" s="28">
         <v>52.4024508223154</v>
       </c>
-      <c r="F4" s="24">
+      <c r="F4" s="30">
         <v>88.6810706223799</v>
       </c>
-      <c r="G4" s="26">
+      <c r="G4" s="32">
         <v>72.557239600129</v>
       </c>
     </row>
@@ -3503,16 +5837,16 @@
           <t>OCCIDENTE</t>
         </is>
       </c>
-      <c r="D5" s="20">
+      <c r="D5" s="26">
         <v>45.9178987969511</v>
       </c>
-      <c r="E5" s="22">
+      <c r="E5" s="28">
         <v>32.1425291578657</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="30">
         <v>110.202957112683</v>
       </c>
-      <c r="G5" s="26">
+      <c r="G5" s="32">
         <v>78.0604279548168</v>
       </c>
     </row>
@@ -3530,16 +5864,16 @@
           <t>OCCIDENTE</t>
         </is>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="26">
         <v>11.3869278068777</v>
       </c>
-      <c r="E6" s="22">
+      <c r="E6" s="28">
         <v>11.3869278068777</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="30">
         <v>136.643133682532</v>
       </c>
-      <c r="G6" s="26">
+      <c r="G6" s="32">
         <v>56.9346390343885</v>
       </c>
     </row>
@@ -3557,103 +5891,103 @@
           <t>OCCIDENTE</t>
         </is>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="26">
         <v>26.8276324614353</v>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="28">
         <v>13.4138162307176</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="30">
         <v>80.4828973843058</v>
       </c>
-      <c r="G7" s="26">
+      <c r="G7" s="32">
         <v>93.8967136150235</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="25" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D8" s="21">
+      <c r="D8" s="27">
         <v>41.9235511713933</v>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="29">
         <v>34.5252774352651</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="31">
         <v>91.2453760789149</v>
       </c>
-      <c r="G8" s="27">
+      <c r="G8" s="33">
         <v>65.3514180024661</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="25" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="25" t="inlineStr">
         <is>
           <t>TOTAL SUBREGIÓN OCCIDENTE</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="D9" s="21">
+      <c r="C9" s="25" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D9" s="27">
         <v>117.809626729498</v>
       </c>
-      <c r="E9" s="23">
+      <c r="E9" s="29">
         <v>39.8604000212589</v>
       </c>
-      <c r="F9" s="25">
+      <c r="F9" s="31">
         <v>104.522826722412</v>
       </c>
-      <c r="G9" s="27">
+      <c r="G9" s="33">
         <v>66.4340000354315</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="25" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>TOTAL DEPARTAMENTO (ANTIOQUIA)</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="25" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D10" s="21">
+      <c r="D10" s="27">
         <v>506.74242087463</v>
       </c>
-      <c r="E10" s="23">
+      <c r="E10" s="29">
         <v>25.3306260114209</v>
       </c>
-      <c r="F10" s="25">
+      <c r="F10" s="31">
         <v>276.471875355423</v>
       </c>
-      <c r="G10" s="27">
+      <c r="G10" s="33">
         <v>71.9216577862736</v>
       </c>
     </row>
@@ -3669,59 +6003,59 @@
   <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="44.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="7.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="45.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="35" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="35" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="35" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="35" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="35" t="inlineStr">
         <is>
           <t>Víctimas por ocurrencia</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="35" t="inlineStr">
         <is>
           <t>Víctimas por declaración</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="35" t="inlineStr">
         <is>
           <t>Víctimas por ubicación</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="35" t="inlineStr">
         <is>
           <t>Sujetos de atención</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="35" t="inlineStr">
         <is>
           <t>Eventos</t>
         </is>
@@ -3746,19 +6080,19 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E2" s="28">
+      <c r="E2" s="37">
         <v>2644</v>
       </c>
-      <c r="F2" s="30">
+      <c r="F2" s="39">
         <v>1751</v>
       </c>
-      <c r="G2" s="32">
+      <c r="G2" s="41">
         <v>1328</v>
       </c>
-      <c r="H2" s="34">
+      <c r="H2" s="43">
         <v>1051</v>
       </c>
-      <c r="I2" s="36">
+      <c r="I2" s="45">
         <v>2720</v>
       </c>
     </row>
@@ -3781,19 +6115,19 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E3" s="28">
+      <c r="E3" s="37">
         <v>13875</v>
       </c>
-      <c r="F3" s="30">
+      <c r="F3" s="39">
         <v>5438</v>
       </c>
-      <c r="G3" s="32">
+      <c r="G3" s="41">
         <v>6032</v>
       </c>
-      <c r="H3" s="34">
+      <c r="H3" s="43">
         <v>5307</v>
       </c>
-      <c r="I3" s="36">
+      <c r="I3" s="45">
         <v>14730</v>
       </c>
     </row>
@@ -3816,19 +6150,19 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E4" s="28">
+      <c r="E4" s="37">
         <v>55034</v>
       </c>
-      <c r="F4" s="30">
+      <c r="F4" s="39">
         <v>24903</v>
       </c>
-      <c r="G4" s="32">
+      <c r="G4" s="41">
         <v>21462</v>
       </c>
-      <c r="H4" s="34">
+      <c r="H4" s="43">
         <v>19115</v>
       </c>
-      <c r="I4" s="36">
+      <c r="I4" s="45">
         <v>60586</v>
       </c>
     </row>
@@ -3851,19 +6185,19 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E5" s="28">
+      <c r="E5" s="37">
         <v>22256</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="39">
         <v>14343</v>
       </c>
-      <c r="G5" s="32">
+      <c r="G5" s="41">
         <v>12373</v>
       </c>
-      <c r="H5" s="34">
+      <c r="H5" s="43">
         <v>10746</v>
       </c>
-      <c r="I5" s="36">
+      <c r="I5" s="45">
         <v>23929</v>
       </c>
     </row>
@@ -3886,19 +6220,19 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E6" s="28">
+      <c r="E6" s="37">
         <v>19417</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="39">
         <v>11689</v>
       </c>
-      <c r="G6" s="32">
+      <c r="G6" s="41">
         <v>8624</v>
       </c>
-      <c r="H6" s="34">
+      <c r="H6" s="43">
         <v>7921</v>
       </c>
-      <c r="I6" s="36">
+      <c r="I6" s="45">
         <v>22243</v>
       </c>
     </row>
@@ -3921,56 +6255,56 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E7" s="28">
+      <c r="E7" s="37">
         <v>9441</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="39">
         <v>6219</v>
       </c>
-      <c r="G7" s="32">
+      <c r="G7" s="41">
         <v>4099</v>
       </c>
-      <c r="H7" s="34">
+      <c r="H7" s="43">
         <v>3760</v>
       </c>
-      <c r="I7" s="36">
+      <c r="I7" s="45">
         <v>9860</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="36" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="36" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="36" t="inlineStr">
         <is>
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="38">
         <v>122667</v>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="40">
         <v>64343</v>
       </c>
-      <c r="G8" s="33">
+      <c r="G8" s="42">
         <v>53918</v>
       </c>
-      <c r="H8" s="35">
+      <c r="H8" s="44">
         <v>47900</v>
       </c>
-      <c r="I8" s="37">
+      <c r="I8" s="46">
         <v>134068</v>
       </c>
     </row>
@@ -3986,23 +6320,23 @@
   <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="87.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="29.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="88.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="48" t="inlineStr">
         <is>
           <t>Hecho victimizante</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="48" t="inlineStr">
         <is>
           <t>Víctimas por ocurrencia</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="48" t="inlineStr">
         <is>
           <t>Proporción sobre el total (%)</t>
         </is>
@@ -4014,10 +6348,10 @@
           <t>Desplazamiento forzado</t>
         </is>
       </c>
-      <c r="B2" s="38">
+      <c r="B2" s="49">
         <v>97659</v>
       </c>
-      <c r="C2" s="39">
+      <c r="C2" s="50">
         <v>0.796130988774487</v>
       </c>
     </row>
@@ -4027,10 +6361,10 @@
           <t>Homicidio (Conflicto)</t>
         </is>
       </c>
-      <c r="B3" s="38">
+      <c r="B3" s="49">
         <v>10715</v>
       </c>
-      <c r="C3" s="39">
+      <c r="C3" s="50">
         <v>0.0873503061132986</v>
       </c>
     </row>
@@ -4040,10 +6374,10 @@
           <t>Amenaza (Conflicto)</t>
         </is>
       </c>
-      <c r="B4" s="38">
+      <c r="B4" s="49">
         <v>6343</v>
       </c>
-      <c r="C4" s="39">
+      <c r="C4" s="50">
         <v>0.0517090986165798</v>
       </c>
     </row>
@@ -4053,10 +6387,10 @@
           <t>Desaparición forzada</t>
         </is>
       </c>
-      <c r="B5" s="38">
+      <c r="B5" s="49">
         <v>2445</v>
       </c>
-      <c r="C5" s="39">
+      <c r="C5" s="50">
         <v>0.0199320110543178</v>
       </c>
     </row>
@@ -4066,10 +6400,10 @@
           <t>Sin informacion (Conflicto)</t>
         </is>
       </c>
-      <c r="B6" s="38">
+      <c r="B6" s="49">
         <v>1771</v>
       </c>
-      <c r="C6" s="39">
+      <c r="C6" s="50">
         <v>0.0144374607677697</v>
       </c>
     </row>
@@ -4079,10 +6413,10 @@
           <t>Confinamiento (Conflicto)</t>
         </is>
       </c>
-      <c r="B7" s="38">
+      <c r="B7" s="49">
         <v>1097</v>
       </c>
-      <c r="C7" s="39">
+      <c r="C7" s="50">
         <v>0.00894291048122152</v>
       </c>
     </row>
@@ -4092,10 +6426,10 @@
           <t>Perdida de Bienes Muebles o Inmuebles</t>
         </is>
       </c>
-      <c r="B8" s="38">
+      <c r="B8" s="49">
         <v>909</v>
       </c>
-      <c r="C8" s="39">
+      <c r="C8" s="50">
         <v>0.00741030595025557</v>
       </c>
     </row>
@@ -4105,10 +6439,10 @@
           <t>Secuestro (Conflicto)</t>
         </is>
       </c>
-      <c r="B9" s="38">
+      <c r="B9" s="49">
         <v>536</v>
       </c>
-      <c r="C9" s="39">
+      <c r="C9" s="50">
         <v>0.00436955334360504</v>
       </c>
     </row>
@@ -4118,10 +6452,10 @@
           <t>Acto terrorista / Atentados / Combates / Enfrentamientos / Hostigamientos</t>
         </is>
       </c>
-      <c r="B10" s="38">
+      <c r="B10" s="49">
         <v>289</v>
       </c>
-      <c r="C10" s="39">
+      <c r="C10" s="50">
         <v>0.00235597185877212</v>
       </c>
     </row>
@@ -4131,10 +6465,10 @@
           <t>Delitos contra la libertad y la integridad sexual en desarrollo del conflicto armado</t>
         </is>
       </c>
-      <c r="B11" s="38">
+      <c r="B11" s="49">
         <v>231</v>
       </c>
-      <c r="C11" s="39">
+      <c r="C11" s="50">
         <v>0.00188314705666561</v>
       </c>
     </row>
@@ -4144,10 +6478,10 @@
           <t>Minas Antipersonal, Munición sin Explotar y Artefacto Explosivo improvisado</t>
         </is>
       </c>
-      <c r="B12" s="38">
+      <c r="B12" s="49">
         <v>165</v>
       </c>
-      <c r="C12" s="39">
+      <c r="C12" s="50">
         <v>0.00134510504047543</v>
       </c>
     </row>
@@ -4157,10 +6491,10 @@
           <t>Lesiones Personales Fisicas</t>
         </is>
       </c>
-      <c r="B13" s="38">
+      <c r="B13" s="49">
         <v>162</v>
       </c>
-      <c r="C13" s="39">
+      <c r="C13" s="50">
         <v>0.00132064858519406</v>
       </c>
     </row>
@@ -4170,10 +6504,10 @@
           <t>Vinculación de Niños Niñas y Adolescentes a Actividades Relacionadas con grupos armados</t>
         </is>
       </c>
-      <c r="B14" s="38">
+      <c r="B14" s="49">
         <v>115</v>
       </c>
-      <c r="C14" s="39">
+      <c r="C14" s="50">
         <v>0.000937497452452575</v>
       </c>
     </row>
@@ -4183,10 +6517,10 @@
           <t>Lesiones Personales Psicologicas</t>
         </is>
       </c>
-      <c r="B15" s="38">
+      <c r="B15" s="49">
         <v>111</v>
       </c>
-      <c r="C15" s="39">
+      <c r="C15" s="50">
         <v>0.000904888845410746</v>
       </c>
     </row>
@@ -4196,10 +6530,10 @@
           <t>Tortura (Conflicto)</t>
         </is>
       </c>
-      <c r="B16" s="38">
+      <c r="B16" s="49">
         <v>82</v>
       </c>
-      <c r="C16" s="39">
+      <c r="C16" s="50">
         <v>0.000668476444357488</v>
       </c>
     </row>
@@ -4209,10 +6543,10 @@
           <t>Abandono o Despojo Forzado de Tierras</t>
         </is>
       </c>
-      <c r="B17" s="38">
+      <c r="B17" s="49">
         <v>37</v>
       </c>
-      <c r="C17" s="39">
+      <c r="C17" s="50">
         <v>0.000301629615136915</v>
       </c>
     </row>
@@ -4222,10 +6556,10 @@
           <t>TOTAL PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="B18" s="38">
+      <c r="B18" s="49">
         <v>122667</v>
       </c>
-      <c r="C18" s="39">
+      <c r="C18" s="50">
         <v>1</v>
       </c>
     </row>
@@ -4241,47 +6575,47 @@
   <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="44.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="45.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="52" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="52" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="52" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="52" t="inlineStr">
         <is>
           <t>Número de solicitudes</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="52" t="inlineStr">
         <is>
           <t>Número de predios</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="52" t="inlineStr">
         <is>
           <t>Número de titulares</t>
         </is>
@@ -4306,13 +6640,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E2" s="40">
+      <c r="E2" s="54">
         <v>20</v>
       </c>
-      <c r="F2" s="42">
+      <c r="F2" s="56">
         <v>17</v>
       </c>
-      <c r="G2" s="44">
+      <c r="G2" s="58">
         <v>17</v>
       </c>
     </row>
@@ -4335,13 +6669,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E3" s="40">
+      <c r="E3" s="54">
         <v>141</v>
       </c>
-      <c r="F3" s="42">
+      <c r="F3" s="56">
         <v>129</v>
       </c>
-      <c r="G3" s="44">
+      <c r="G3" s="58">
         <v>131</v>
       </c>
     </row>
@@ -4364,13 +6698,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E4" s="40">
+      <c r="E4" s="54">
         <v>677</v>
       </c>
-      <c r="F4" s="42">
+      <c r="F4" s="56">
         <v>578</v>
       </c>
-      <c r="G4" s="44">
+      <c r="G4" s="58">
         <v>560</v>
       </c>
     </row>
@@ -4393,13 +6727,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E5" s="40">
+      <c r="E5" s="54">
         <v>212</v>
       </c>
-      <c r="F5" s="42">
+      <c r="F5" s="56">
         <v>173</v>
       </c>
-      <c r="G5" s="44">
+      <c r="G5" s="58">
         <v>188</v>
       </c>
     </row>
@@ -4422,13 +6756,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E6" s="40">
+      <c r="E6" s="54">
         <v>54</v>
       </c>
-      <c r="F6" s="42">
+      <c r="F6" s="56">
         <v>49</v>
       </c>
-      <c r="G6" s="44">
+      <c r="G6" s="58">
         <v>49</v>
       </c>
     </row>
@@ -4451,106 +6785,106 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E7" s="40">
+      <c r="E7" s="54">
         <v>49</v>
       </c>
-      <c r="F7" s="42">
+      <c r="F7" s="56">
         <v>38</v>
       </c>
-      <c r="G7" s="44">
+      <c r="G7" s="58">
         <v>40</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="53" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="53" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="53" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="53" t="inlineStr">
         <is>
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E8" s="41">
+      <c r="E8" s="55">
         <v>1153</v>
       </c>
-      <c r="F8" s="43">
+      <c r="F8" s="57">
         <v>984</v>
       </c>
-      <c r="G8" s="45">
+      <c r="G8" s="59">
         <v>985</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="53" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="53" t="inlineStr">
         <is>
           <t>TOTAL SUBREGIÓN OCCIDENTE</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="C9" s="53" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D9" s="53" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E9" s="41">
+      <c r="E9" s="55">
         <v>1505</v>
       </c>
-      <c r="F9" s="43">
+      <c r="F9" s="57">
         <v>1299</v>
       </c>
-      <c r="G9" s="45">
+      <c r="G9" s="59">
         <v>1293</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="53" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="53" t="inlineStr">
         <is>
           <t>TOTAL DEPARTAMENTO (ANTIOQUIA)</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="53" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="53" t="inlineStr">
         <is>
           <t>DEPARTAMENTO DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E10" s="41">
+      <c r="E10" s="55">
         <v>27352</v>
       </c>
-      <c r="F10" s="43">
+      <c r="F10" s="57">
         <v>24834</v>
       </c>
-      <c r="G10" s="45">
+      <c r="G10" s="59">
         <v>23637</v>
       </c>
     </row>
@@ -4566,47 +6900,47 @@
   <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="44.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="36.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="45.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="37.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="61" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="61" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="61" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="61" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="61" t="inlineStr">
         <is>
           <t>Número de solicitudes</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="61" t="inlineStr">
         <is>
           <t>Población (2025)</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="61" t="inlineStr">
         <is>
           <t>Tasa de solicitudes (por 1.000 hab.)</t>
         </is>
@@ -4631,13 +6965,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E2" s="46">
+      <c r="E2" s="63">
         <v>20</v>
       </c>
-      <c r="F2" s="48">
+      <c r="F2" s="65">
         <v>2807</v>
       </c>
-      <c r="G2" s="50">
+      <c r="G2" s="67">
         <v>7.12504453152832</v>
       </c>
     </row>
@@ -4660,13 +6994,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E3" s="46">
+      <c r="E3" s="63">
         <v>141</v>
       </c>
-      <c r="F3" s="48">
+      <c r="F3" s="65">
         <v>15470</v>
       </c>
-      <c r="G3" s="50">
+      <c r="G3" s="67">
         <v>9.11441499676794</v>
       </c>
     </row>
@@ -4689,13 +7023,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E4" s="46">
+      <c r="E4" s="63">
         <v>677</v>
       </c>
-      <c r="F4" s="48">
+      <c r="F4" s="65">
         <v>24808</v>
       </c>
-      <c r="G4" s="50">
+      <c r="G4" s="67">
         <v>27.2895840051596</v>
       </c>
     </row>
@@ -4718,13 +7052,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E5" s="46">
+      <c r="E5" s="63">
         <v>212</v>
       </c>
-      <c r="F5" s="48">
+      <c r="F5" s="65">
         <v>21778</v>
       </c>
-      <c r="G5" s="50">
+      <c r="G5" s="67">
         <v>9.73459454495362</v>
       </c>
     </row>
@@ -4747,13 +7081,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E6" s="46">
+      <c r="E6" s="63">
         <v>54</v>
       </c>
-      <c r="F6" s="48">
+      <c r="F6" s="65">
         <v>8782</v>
       </c>
-      <c r="G6" s="50">
+      <c r="G6" s="67">
         <v>6.14894101571396</v>
       </c>
     </row>
@@ -4776,106 +7110,106 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E7" s="46">
+      <c r="E7" s="63">
         <v>49</v>
       </c>
-      <c r="F7" s="48">
+      <c r="F7" s="65">
         <v>7455</v>
       </c>
-      <c r="G7" s="50">
+      <c r="G7" s="67">
         <v>6.57276995305164</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="62" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="62" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="62" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="62" t="inlineStr">
         <is>
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E8" s="47">
+      <c r="E8" s="64">
         <v>1153</v>
       </c>
-      <c r="F8" s="49">
+      <c r="F8" s="66">
         <v>81100</v>
       </c>
-      <c r="G8" s="51">
+      <c r="G8" s="68">
         <v>14.2170160295931</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="62" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="62" t="inlineStr">
         <is>
           <t>TOTAL SUBREGIÓN OCCIDENTE</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="C9" s="62" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D9" s="62" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E9" s="47">
+      <c r="E9" s="64">
         <v>1505</v>
       </c>
-      <c r="F9" s="49">
+      <c r="F9" s="66">
         <v>225788</v>
       </c>
-      <c r="G9" s="51">
+      <c r="G9" s="68">
         <v>6.66554467022162</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="62" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="62" t="inlineStr">
         <is>
           <t>TOTAL DEPARTAMENTO (ANTIOQUIA)</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="62" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="62" t="inlineStr">
         <is>
           <t>DEPARTAMENTO DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E10" s="47">
+      <c r="E10" s="64">
         <v>27352</v>
       </c>
-      <c r="F10" s="49">
+      <c r="F10" s="66">
         <v>6821720</v>
       </c>
-      <c r="G10" s="51">
+      <c r="G10" s="68">
         <v>4.00954597960632</v>
       </c>
     </row>
@@ -4891,47 +7225,47 @@
   <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="70" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="70" t="inlineStr">
         <is>
           <t>Periodo</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="70" t="inlineStr">
         <is>
           <t>N respuestas</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="70" t="inlineStr">
         <is>
           <t>Muy seguro (%)</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="70" t="inlineStr">
         <is>
           <t>Seguro (%)</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="70" t="inlineStr">
         <is>
           <t>Inseguro (%)</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="70" t="inlineStr">
         <is>
           <t>Muy inseguro (%)</t>
         </is>
@@ -4948,19 +7282,19 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="C2" s="56">
+      <c r="C2" s="75">
         <v>192</v>
       </c>
-      <c r="D2" s="52">
+      <c r="D2" s="71">
         <v>0.0947998580455986</v>
       </c>
-      <c r="E2" s="53">
+      <c r="E2" s="72">
         <v>0.797602705838581</v>
       </c>
-      <c r="F2" s="54">
+      <c r="F2" s="73">
         <v>0.100453589266174</v>
       </c>
-      <c r="G2" s="55">
+      <c r="G2" s="74">
         <v>0.00714384684964663</v>
       </c>
     </row>
@@ -4975,19 +7309,19 @@
           <t>2019 (1)</t>
         </is>
       </c>
-      <c r="C3" s="56">
+      <c r="C3" s="75">
         <v>192</v>
       </c>
-      <c r="D3" s="52">
+      <c r="D3" s="71">
         <v>0.200435006165625</v>
       </c>
-      <c r="E3" s="53">
+      <c r="E3" s="72">
         <v>0.695275675926725</v>
       </c>
-      <c r="F3" s="54">
+      <c r="F3" s="73">
         <v>0.0850064894389614</v>
       </c>
-      <c r="G3" s="55">
+      <c r="G3" s="74">
         <v>0.0192828284686885</v>
       </c>
     </row>
@@ -5002,19 +7336,19 @@
           <t>2019 (2)</t>
         </is>
       </c>
-      <c r="C4" s="56">
+      <c r="C4" s="75">
         <v>192</v>
       </c>
-      <c r="D4" s="52">
+      <c r="D4" s="71">
         <v>0.158593699873702</v>
       </c>
-      <c r="E4" s="53">
+      <c r="E4" s="72">
         <v>0.777018281646666</v>
       </c>
-      <c r="F4" s="54">
+      <c r="F4" s="73">
         <v>0.059991845554648</v>
       </c>
-      <c r="G4" s="55">
+      <c r="G4" s="74">
         <v>0.00439617292498392</v>
       </c>
     </row>
@@ -5029,19 +7363,19 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="C5" s="56">
+      <c r="C5" s="75">
         <v>216</v>
       </c>
-      <c r="D5" s="52">
+      <c r="D5" s="71">
         <v>0.16325991432909</v>
       </c>
-      <c r="E5" s="53">
+      <c r="E5" s="72">
         <v>0.730886822742361</v>
       </c>
-      <c r="F5" s="54">
+      <c r="F5" s="73">
         <v>0.0813239884978159</v>
       </c>
-      <c r="G5" s="55">
+      <c r="G5" s="74">
         <v>0.0245292744307328</v>
       </c>
     </row>
@@ -5056,19 +7390,19 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="C6" s="56">
+      <c r="C6" s="75">
         <v>216</v>
       </c>
-      <c r="D6" s="52">
+      <c r="D6" s="71">
         <v>0.121797177183111</v>
       </c>
-      <c r="E6" s="53">
+      <c r="E6" s="72">
         <v>0.757828618917356</v>
       </c>
-      <c r="F6" s="54">
+      <c r="F6" s="73">
         <v>0.0851268575837551</v>
       </c>
-      <c r="G6" s="55">
+      <c r="G6" s="74">
         <v>0.0352473463157775</v>
       </c>
     </row>
@@ -5083,19 +7417,19 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="C7" s="56">
+      <c r="C7" s="75">
         <v>216</v>
       </c>
-      <c r="D7" s="52">
+      <c r="D7" s="71">
         <v>0.0573389785624819</v>
       </c>
-      <c r="E7" s="53">
+      <c r="E7" s="72">
         <v>0.823573143035944</v>
       </c>
-      <c r="F7" s="54">
+      <c r="F7" s="73">
         <v>0.106447483655135</v>
       </c>
-      <c r="G7" s="55">
+      <c r="G7" s="74">
         <v>0.0126403947464395</v>
       </c>
     </row>
@@ -5110,19 +7444,19 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="C8" s="56">
+      <c r="C8" s="75">
         <v>208</v>
       </c>
-      <c r="D8" s="52">
+      <c r="D8" s="71">
         <v>0.0975993518758601</v>
       </c>
-      <c r="E8" s="53">
+      <c r="E8" s="72">
         <v>0.843901548536765</v>
       </c>
-      <c r="F8" s="54">
+      <c r="F8" s="73">
         <v>0.0584990995873746</v>
       </c>
-      <c r="G8" s="55">
+      <c r="G8" s="74">
         <v>0</v>
       </c>
     </row>
@@ -5137,19 +7471,19 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="C9" s="56">
+      <c r="C9" s="75">
         <v>216</v>
       </c>
-      <c r="D9" s="52">
+      <c r="D9" s="71">
         <v>0.0639974638436177</v>
       </c>
-      <c r="E9" s="53">
+      <c r="E9" s="72">
         <v>0.85274827805597</v>
       </c>
-      <c r="F9" s="54">
+      <c r="F9" s="73">
         <v>0.0816031524493063</v>
       </c>
-      <c r="G9" s="55">
+      <c r="G9" s="74">
         <v>0.00165110565110566</v>
       </c>
     </row>
@@ -5165,47 +7499,47 @@
   <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="77" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="77" t="inlineStr">
         <is>
           <t>Periodo</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="77" t="inlineStr">
         <is>
           <t>N respuestas</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="77" t="inlineStr">
         <is>
           <t>Más seguro (%)</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="77" t="inlineStr">
         <is>
           <t>Menos seguro (%)</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="77" t="inlineStr">
         <is>
           <t>Igual (%)</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="77" t="inlineStr">
         <is>
           <t>No sabe/No responde (%)</t>
         </is>
@@ -5222,19 +7556,19 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="C2" s="61">
+      <c r="C2" s="82">
         <v>192</v>
       </c>
-      <c r="D2" s="57">
+      <c r="D2" s="78">
         <v>0.156615135568165</v>
       </c>
-      <c r="E2" s="58">
+      <c r="E2" s="79">
         <v>0.0757713606053115</v>
       </c>
-      <c r="F2" s="59">
+      <c r="F2" s="80">
         <v>0.749233371399697</v>
       </c>
-      <c r="G2" s="60">
+      <c r="G2" s="81">
         <v>0.0183801324268259</v>
       </c>
     </row>
@@ -5249,19 +7583,19 @@
           <t>2019 (1)</t>
         </is>
       </c>
-      <c r="C3" s="61">
+      <c r="C3" s="82">
         <v>192</v>
       </c>
-      <c r="D3" s="57">
+      <c r="D3" s="78">
         <v>0.301885949617252</v>
       </c>
-      <c r="E3" s="58">
+      <c r="E3" s="79">
         <v>0.0858598919488171</v>
       </c>
-      <c r="F3" s="59">
+      <c r="F3" s="80">
         <v>0.610522936092464</v>
       </c>
-      <c r="G3" s="60">
+      <c r="G3" s="81">
         <v>0.00173122234146641</v>
       </c>
     </row>
@@ -5276,19 +7610,19 @@
           <t>2019 (2)</t>
         </is>
       </c>
-      <c r="C4" s="61">
+      <c r="C4" s="82">
         <v>192</v>
       </c>
-      <c r="D4" s="57">
+      <c r="D4" s="78">
         <v>0.164687844197492</v>
       </c>
-      <c r="E4" s="58">
+      <c r="E4" s="79">
         <v>0.0977782875358726</v>
       </c>
-      <c r="F4" s="59">
+      <c r="F4" s="80">
         <v>0.720187724023594</v>
       </c>
-      <c r="G4" s="60">
+      <c r="G4" s="81">
         <v>0.0173461442430418</v>
       </c>
     </row>
@@ -5303,19 +7637,19 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="C5" s="61">
+      <c r="C5" s="82">
         <v>216</v>
       </c>
-      <c r="D5" s="57">
+      <c r="D5" s="78">
         <v>0.303376727179447</v>
       </c>
-      <c r="E5" s="58">
+      <c r="E5" s="79">
         <v>0.0896305540471879</v>
       </c>
-      <c r="F5" s="59">
+      <c r="F5" s="80">
         <v>0.60383980918569</v>
       </c>
-      <c r="G5" s="60">
+      <c r="G5" s="81">
         <v>0.00315290958767506</v>
       </c>
     </row>
@@ -5330,19 +7664,19 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="C6" s="61">
+      <c r="C6" s="82">
         <v>216</v>
       </c>
-      <c r="D6" s="57">
+      <c r="D6" s="78">
         <v>0.237043264074387</v>
       </c>
-      <c r="E6" s="58">
+      <c r="E6" s="79">
         <v>0.082360543811087</v>
       </c>
-      <c r="F6" s="59">
+      <c r="F6" s="80">
         <v>0.670215058106377</v>
       </c>
-      <c r="G6" s="60">
+      <c r="G6" s="81">
         <v>0.0103811340081482</v>
       </c>
     </row>
@@ -5357,19 +7691,19 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="C7" s="61">
+      <c r="C7" s="82">
         <v>216</v>
       </c>
-      <c r="D7" s="57">
+      <c r="D7" s="78">
         <v>0.160952599661839</v>
       </c>
-      <c r="E7" s="58">
+      <c r="E7" s="79">
         <v>0.0694476033864472</v>
       </c>
-      <c r="F7" s="59">
+      <c r="F7" s="80">
         <v>0.769599796951713</v>
       </c>
-      <c r="G7" s="60">
+      <c r="G7" s="81">
         <v>0</v>
       </c>
     </row>
@@ -5384,19 +7718,19 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="C8" s="61">
+      <c r="C8" s="82">
         <v>208</v>
       </c>
-      <c r="D8" s="57">
+      <c r="D8" s="78">
         <v>0.227319863708867</v>
       </c>
-      <c r="E8" s="58">
+      <c r="E8" s="79">
         <v>0.0259327818683812</v>
       </c>
-      <c r="F8" s="59">
+      <c r="F8" s="80">
         <v>0.729751059180749</v>
       </c>
-      <c r="G8" s="60">
+      <c r="G8" s="81">
         <v>0.0169962952420027</v>
       </c>
     </row>
@@ -5411,19 +7745,19 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="C9" s="61">
+      <c r="C9" s="82">
         <v>216</v>
       </c>
-      <c r="D9" s="57">
+      <c r="D9" s="78">
         <v>0.261064248987326</v>
       </c>
-      <c r="E9" s="58">
+      <c r="E9" s="79">
         <v>0.0392630441861211</v>
       </c>
-      <c r="F9" s="59">
+      <c r="F9" s="80">
         <v>0.699672706826553</v>
       </c>
-      <c r="G9" s="60">
+      <c r="G9" s="81">
         <v>0</v>
       </c>
     </row>
